--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2127,6 +2127,1578 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121635201</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56264</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>455851</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6215609</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>04:50</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121635161</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56271</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>455851</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6215609</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121635190</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56264</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>456110</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6215684</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>00:40</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121635239</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56248</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dokumentation efterfrågas</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>455851</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6215609</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>04:50</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121635231</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56248</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Dokumentation efterfrågas</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>456110</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6215684</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>00:40</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121635177</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56267</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100111</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pipistrellus nathusii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>456110</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6215684</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>00:40</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121635228</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56250</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>455851</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6215609</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>04:50</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121635214</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56257</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>455851</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6215609</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121635219</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56250</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>456110</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6215684</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>00:40</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121635169</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56269</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>455851</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6215609</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121635164</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56269</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>456110</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6215684</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>00:40</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121635184</v>
+      </c>
+      <c r="B25" t="n">
+        <v>56267</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100111</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pipistrellus nathusii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>455851</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6215609</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -2130,10 +2130,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121635201</v>
+        <v>121635195</v>
       </c>
       <c r="B14" t="n">
-        <v>56264</v>
+        <v>56265</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2219,22 +2219,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2264,7 +2264,7 @@
         <v>121635161</v>
       </c>
       <c r="B15" t="n">
-        <v>56271</v>
+        <v>56272</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2392,10 +2392,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121635190</v>
+        <v>121635217</v>
       </c>
       <c r="B16" t="n">
-        <v>56264</v>
+        <v>56258</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2408,26 +2408,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R16" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2486,17 +2486,17 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2523,14 +2523,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121635239</v>
+        <v>121635219</v>
       </c>
       <c r="B17" t="n">
-        <v>56248</v>
+        <v>56251</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2539,26 +2539,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R17" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2617,17 +2617,17 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2654,37 +2654,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121635231</v>
+        <v>121635177</v>
       </c>
       <c r="B18" t="n">
-        <v>56248</v>
+        <v>56268</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100015</v>
+        <v>100111</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121635177</v>
+        <v>121635228</v>
       </c>
       <c r="B19" t="n">
-        <v>56267</v>
+        <v>56251</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2797,30 +2797,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R19" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2879,17 +2879,17 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121635228</v>
+        <v>121635184</v>
       </c>
       <c r="B20" t="n">
-        <v>56250</v>
+        <v>56268</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2928,30 +2928,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3005,22 +3005,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121635214</v>
+        <v>121635190</v>
       </c>
       <c r="B21" t="n">
-        <v>56257</v>
+        <v>56265</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3063,26 +3063,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3106,13 +3106,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R21" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3136,22 +3136,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3178,14 +3178,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121635219</v>
+        <v>121635239</v>
       </c>
       <c r="B22" t="n">
-        <v>56250</v>
+        <v>56249</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3194,26 +3194,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R22" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3272,17 +3272,17 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3309,42 +3309,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121635169</v>
+        <v>121635231</v>
       </c>
       <c r="B23" t="n">
-        <v>56269</v>
+        <v>56249</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205995</v>
+        <v>100015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R23" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3398,22 +3398,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3443,7 +3443,7 @@
         <v>121635164</v>
       </c>
       <c r="B24" t="n">
-        <v>56269</v>
+        <v>56270</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3571,10 +3571,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121635184</v>
+        <v>121635169</v>
       </c>
       <c r="B25" t="n">
-        <v>56267</v>
+        <v>56270</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3587,26 +3587,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -2130,37 +2130,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121635231</v>
+        <v>121635177</v>
       </c>
       <c r="B14" t="n">
-        <v>56249</v>
+        <v>56268</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100015</v>
+        <v>100111</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2254,49 +2254,49 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johanna Kammonen, Isabella Honnér</t>
+          <t>Isabella Honnér, Johanna Kammonen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121635164</v>
+        <v>121635239</v>
       </c>
       <c r="B15" t="n">
-        <v>56270</v>
+        <v>56249</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205995</v>
+        <v>100015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R15" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2355,17 +2355,17 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,10 +2392,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121635169</v>
+        <v>121635228</v>
       </c>
       <c r="B16" t="n">
-        <v>56270</v>
+        <v>56251</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2404,30 +2404,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2523,32 +2523,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121635195</v>
+        <v>121635231</v>
       </c>
       <c r="B17" t="n">
-        <v>56265</v>
+        <v>56249</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100092</v>
+        <v>100015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R17" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2654,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121635214</v>
+        <v>121635161</v>
       </c>
       <c r="B18" t="n">
-        <v>56258</v>
+        <v>56272</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2666,30 +2666,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205992</v>
+        <v>206002</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2778,17 +2778,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johanna Kammonen, Isabella Honnér</t>
+          <t>Isabella Honnér, Johanna Kammonen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121635228</v>
+        <v>121635184</v>
       </c>
       <c r="B19" t="n">
-        <v>56251</v>
+        <v>56268</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2797,30 +2797,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2874,22 +2874,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2909,39 +2909,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johanna Kammonen, Isabella Honnér</t>
+          <t>Isabella Honnér, Johanna Kammonen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121635234</v>
+        <v>121635195</v>
       </c>
       <c r="B20" t="n">
-        <v>56249</v>
+        <v>56265</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100015</v>
+        <v>100092</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3040,17 +3040,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johanna Kammonen, Isabella Honnér</t>
+          <t>Isabella Honnér, Johanna Kammonen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121635219</v>
+        <v>121635164</v>
       </c>
       <c r="B21" t="n">
-        <v>56251</v>
+        <v>56270</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3059,30 +3059,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3171,17 +3171,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johanna Kammonen, Isabella Honnér</t>
+          <t>Isabella Honnér, Johanna Kammonen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121635177</v>
+        <v>121635214</v>
       </c>
       <c r="B22" t="n">
-        <v>56268</v>
+        <v>56258</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3194,21 +3194,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R22" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3267,22 +3267,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3440,10 +3440,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121635184</v>
+        <v>121635219</v>
       </c>
       <c r="B24" t="n">
-        <v>56268</v>
+        <v>56251</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3452,30 +3452,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3499,13 +3499,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R24" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3529,22 +3529,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121635161</v>
+        <v>121635169</v>
       </c>
       <c r="B25" t="n">
-        <v>56272</v>
+        <v>56270</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3583,30 +3583,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -2654,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121635161</v>
+        <v>121635184</v>
       </c>
       <c r="B18" t="n">
-        <v>56272</v>
+        <v>56268</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2666,30 +2666,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>206002</v>
+        <v>100111</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121635184</v>
+        <v>121635161</v>
       </c>
       <c r="B19" t="n">
-        <v>56268</v>
+        <v>56272</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2797,30 +2797,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100111</v>
+        <v>206002</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -2130,42 +2130,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121635177</v>
+        <v>121635234</v>
       </c>
       <c r="B14" t="n">
-        <v>56268</v>
+        <v>56249</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100111</v>
+        <v>100015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R14" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,22 +2219,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,37 +2261,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121635239</v>
+        <v>121635177</v>
       </c>
       <c r="B15" t="n">
-        <v>56249</v>
+        <v>56268</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100015</v>
+        <v>100111</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R15" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2355,17 +2355,17 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2654,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121635184</v>
+        <v>121635201</v>
       </c>
       <c r="B18" t="n">
-        <v>56268</v>
+        <v>56265</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2670,26 +2670,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2743,22 +2743,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121635161</v>
+        <v>121635184</v>
       </c>
       <c r="B19" t="n">
-        <v>56272</v>
+        <v>56268</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2797,30 +2797,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>206002</v>
+        <v>100111</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121635195</v>
+        <v>121635164</v>
       </c>
       <c r="B20" t="n">
-        <v>56265</v>
+        <v>56270</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2932,26 +2932,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2975,13 +2975,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R20" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3005,22 +3005,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121635164</v>
+        <v>121635217</v>
       </c>
       <c r="B21" t="n">
-        <v>56270</v>
+        <v>56258</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3063,26 +3063,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3106,13 +3106,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R21" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3141,17 +3141,17 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3178,10 +3178,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121635214</v>
+        <v>121635190</v>
       </c>
       <c r="B22" t="n">
-        <v>56258</v>
+        <v>56265</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3194,26 +3194,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R22" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3267,22 +3267,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3309,10 +3309,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121635190</v>
+        <v>121635169</v>
       </c>
       <c r="B23" t="n">
-        <v>56265</v>
+        <v>56270</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3325,26 +3325,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R23" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3398,22 +3398,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121635169</v>
+        <v>121635161</v>
       </c>
       <c r="B25" t="n">
-        <v>56270</v>
+        <v>56272</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3583,30 +3583,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -2130,42 +2130,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121635234</v>
+        <v>121635217</v>
       </c>
       <c r="B14" t="n">
-        <v>56249</v>
+        <v>56258</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100015</v>
+        <v>205992</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2219,22 +2219,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,10 +2261,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121635177</v>
+        <v>121635228</v>
       </c>
       <c r="B15" t="n">
-        <v>56268</v>
+        <v>56251</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2273,30 +2273,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R15" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2355,17 +2355,17 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,14 +2392,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121635228</v>
+        <v>121635231</v>
       </c>
       <c r="B16" t="n">
-        <v>56251</v>
+        <v>56249</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2408,26 +2408,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R16" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2486,17 +2486,17 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2523,32 +2523,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121635231</v>
+        <v>121635195</v>
       </c>
       <c r="B17" t="n">
-        <v>56249</v>
+        <v>56265</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100015</v>
+        <v>100092</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R17" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2654,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121635201</v>
+        <v>121635161</v>
       </c>
       <c r="B18" t="n">
-        <v>56265</v>
+        <v>56272</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2666,30 +2666,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2743,22 +2743,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121635164</v>
+        <v>121635219</v>
       </c>
       <c r="B20" t="n">
-        <v>56270</v>
+        <v>56251</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2928,30 +2928,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121635217</v>
+        <v>121635177</v>
       </c>
       <c r="B21" t="n">
-        <v>56258</v>
+        <v>56268</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3063,21 +3063,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3106,13 +3106,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R21" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3141,17 +3141,17 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3309,7 +3309,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121635169</v>
+        <v>121635164</v>
       </c>
       <c r="B23" t="n">
         <v>56270</v>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R23" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3398,22 +3398,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3440,14 +3440,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121635219</v>
+        <v>121635234</v>
       </c>
       <c r="B24" t="n">
-        <v>56251</v>
+        <v>56249</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3456,26 +3456,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3499,13 +3499,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R24" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3529,22 +3529,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121635161</v>
+        <v>121635169</v>
       </c>
       <c r="B25" t="n">
-        <v>56272</v>
+        <v>56270</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3583,30 +3583,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -2130,10 +2130,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121635217</v>
+        <v>121635177</v>
       </c>
       <c r="B14" t="n">
-        <v>56258</v>
+        <v>56268</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R14" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2224,17 +2224,17 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,10 +2261,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121635228</v>
+        <v>121635161</v>
       </c>
       <c r="B15" t="n">
-        <v>56251</v>
+        <v>56272</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2277,26 +2277,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,7 +2392,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121635231</v>
+        <v>121635239</v>
       </c>
       <c r="B16" t="n">
         <v>56249</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R16" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2486,17 +2486,17 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2523,7 +2523,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121635195</v>
+        <v>121635201</v>
       </c>
       <c r="B17" t="n">
         <v>56265</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2654,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121635161</v>
+        <v>121635219</v>
       </c>
       <c r="B18" t="n">
-        <v>56272</v>
+        <v>56251</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2670,26 +2670,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2713,13 +2713,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R18" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2743,22 +2743,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121635184</v>
+        <v>121635169</v>
       </c>
       <c r="B19" t="n">
-        <v>56268</v>
+        <v>56270</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2801,26 +2801,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121635219</v>
+        <v>121635217</v>
       </c>
       <c r="B20" t="n">
-        <v>56251</v>
+        <v>56258</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2928,30 +2928,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2975,13 +2975,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R20" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3010,17 +3010,17 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3047,37 +3047,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121635177</v>
+        <v>121635231</v>
       </c>
       <c r="B21" t="n">
-        <v>56268</v>
+        <v>56249</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100111</v>
+        <v>100015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3178,10 +3178,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121635190</v>
+        <v>121635184</v>
       </c>
       <c r="B22" t="n">
-        <v>56265</v>
+        <v>56268</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3194,26 +3194,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R22" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3267,22 +3267,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3309,10 +3309,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121635164</v>
+        <v>121635190</v>
       </c>
       <c r="B23" t="n">
-        <v>56270</v>
+        <v>56265</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3325,26 +3325,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3440,42 +3440,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121635234</v>
+        <v>121635164</v>
       </c>
       <c r="B24" t="n">
-        <v>56249</v>
+        <v>56270</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100015</v>
+        <v>205995</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3499,13 +3499,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R24" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3529,22 +3529,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121635169</v>
+        <v>121635228</v>
       </c>
       <c r="B25" t="n">
-        <v>56270</v>
+        <v>56251</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3583,30 +3583,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3660,22 +3660,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -2130,42 +2130,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121635177</v>
+        <v>121635234</v>
       </c>
       <c r="B14" t="n">
-        <v>56268</v>
+        <v>56249</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100111</v>
+        <v>100015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R14" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,22 +2219,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2392,42 +2392,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121635239</v>
+        <v>121635164</v>
       </c>
       <c r="B16" t="n">
-        <v>56249</v>
+        <v>56270</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100015</v>
+        <v>205995</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R16" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2486,17 +2486,17 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2523,7 +2523,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121635201</v>
+        <v>121635190</v>
       </c>
       <c r="B17" t="n">
         <v>56265</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R17" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2617,17 +2617,17 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2654,7 +2654,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121635219</v>
+        <v>121635228</v>
       </c>
       <c r="B18" t="n">
         <v>56251</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2713,13 +2713,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R18" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2748,17 +2748,17 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121635169</v>
+        <v>121635219</v>
       </c>
       <c r="B19" t="n">
-        <v>56270</v>
+        <v>56251</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2797,30 +2797,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R19" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2874,22 +2874,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121635217</v>
+        <v>121635169</v>
       </c>
       <c r="B20" t="n">
-        <v>56258</v>
+        <v>56270</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2932,26 +2932,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3005,22 +3005,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3047,42 +3047,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121635231</v>
+        <v>121635184</v>
       </c>
       <c r="B21" t="n">
-        <v>56249</v>
+        <v>56268</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100015</v>
+        <v>100111</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3106,13 +3106,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R21" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3136,22 +3136,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3178,10 +3178,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121635184</v>
+        <v>121635195</v>
       </c>
       <c r="B22" t="n">
-        <v>56268</v>
+        <v>56265</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3194,26 +3194,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3309,10 +3309,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121635190</v>
+        <v>121635217</v>
       </c>
       <c r="B23" t="n">
-        <v>56265</v>
+        <v>56258</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3325,26 +3325,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R23" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3403,17 +3403,17 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3440,42 +3440,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121635164</v>
+        <v>121635231</v>
       </c>
       <c r="B24" t="n">
-        <v>56270</v>
+        <v>56249</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205995</v>
+        <v>100015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121635228</v>
+        <v>121635177</v>
       </c>
       <c r="B25" t="n">
-        <v>56251</v>
+        <v>56268</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3583,30 +3583,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3630,13 +3630,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R25" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -2130,14 +2130,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121635234</v>
+        <v>121635228</v>
       </c>
       <c r="B14" t="n">
-        <v>56249</v>
+        <v>56251</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2146,26 +2146,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2219,22 +2219,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,10 +2261,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121635161</v>
+        <v>121635190</v>
       </c>
       <c r="B15" t="n">
-        <v>56272</v>
+        <v>56265</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2273,30 +2273,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R15" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2350,22 +2350,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,7 +2392,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121635164</v>
+        <v>121635169</v>
       </c>
       <c r="B16" t="n">
         <v>56270</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R16" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2481,22 +2481,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2523,10 +2523,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121635190</v>
+        <v>121635219</v>
       </c>
       <c r="B17" t="n">
-        <v>56265</v>
+        <v>56251</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2535,30 +2535,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2654,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121635228</v>
+        <v>121635161</v>
       </c>
       <c r="B18" t="n">
-        <v>56251</v>
+        <v>56272</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2670,26 +2670,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2743,22 +2743,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121635219</v>
+        <v>121635164</v>
       </c>
       <c r="B19" t="n">
-        <v>56251</v>
+        <v>56270</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2797,30 +2797,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2916,10 +2916,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121635169</v>
+        <v>121635214</v>
       </c>
       <c r="B20" t="n">
-        <v>56270</v>
+        <v>56258</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2932,26 +2932,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3178,32 +3178,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121635195</v>
+        <v>121635234</v>
       </c>
       <c r="B22" t="n">
-        <v>56265</v>
+        <v>56249</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100092</v>
+        <v>100015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3309,10 +3309,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121635217</v>
+        <v>121635195</v>
       </c>
       <c r="B23" t="n">
-        <v>56258</v>
+        <v>56265</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3325,26 +3325,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3398,22 +3398,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3440,37 +3440,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121635231</v>
+        <v>121635177</v>
       </c>
       <c r="B24" t="n">
-        <v>56249</v>
+        <v>56268</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100015</v>
+        <v>100111</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3571,37 +3571,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121635177</v>
+        <v>121635231</v>
       </c>
       <c r="B25" t="n">
-        <v>56268</v>
+        <v>56249</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100111</v>
+        <v>100015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -2133,7 +2133,7 @@
         <v>121635228</v>
       </c>
       <c r="B14" t="n">
-        <v>56251</v>
+        <v>56259</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121635190</v>
+        <v>121635184</v>
       </c>
       <c r="B15" t="n">
-        <v>56265</v>
+        <v>56276</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2277,26 +2277,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R15" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2350,22 +2350,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,10 +2392,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121635169</v>
+        <v>121635164</v>
       </c>
       <c r="B16" t="n">
-        <v>56270</v>
+        <v>56278</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R16" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2481,22 +2481,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2526,7 +2526,7 @@
         <v>121635219</v>
       </c>
       <c r="B17" t="n">
-        <v>56251</v>
+        <v>56259</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121635161</v>
+        <v>121635201</v>
       </c>
       <c r="B18" t="n">
-        <v>56272</v>
+        <v>56273</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2666,30 +2666,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2743,22 +2743,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121635164</v>
+        <v>121635217</v>
       </c>
       <c r="B19" t="n">
-        <v>56270</v>
+        <v>56266</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2801,26 +2801,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R19" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2879,17 +2879,17 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2916,37 +2916,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121635214</v>
+        <v>121635239</v>
       </c>
       <c r="B20" t="n">
-        <v>56258</v>
+        <v>56257</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205992</v>
+        <v>100015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3005,22 +3005,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121635184</v>
+        <v>121635190</v>
       </c>
       <c r="B21" t="n">
-        <v>56268</v>
+        <v>56273</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3063,26 +3063,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3106,13 +3106,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R21" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3136,22 +3136,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3178,42 +3178,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121635234</v>
+        <v>121635177</v>
       </c>
       <c r="B22" t="n">
-        <v>56249</v>
+        <v>56276</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100015</v>
+        <v>100111</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R22" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3267,22 +3267,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3309,10 +3309,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121635195</v>
+        <v>121635161</v>
       </c>
       <c r="B23" t="n">
-        <v>56265</v>
+        <v>56280</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3321,30 +3321,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3440,37 +3440,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121635177</v>
+        <v>121635231</v>
       </c>
       <c r="B24" t="n">
-        <v>56268</v>
+        <v>56257</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100111</v>
+        <v>100015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3571,42 +3571,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121635231</v>
+        <v>121635169</v>
       </c>
       <c r="B25" t="n">
-        <v>56249</v>
+        <v>56278</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100015</v>
+        <v>205995</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3630,13 +3630,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R25" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3660,22 +3660,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -2130,10 +2130,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121635228</v>
+        <v>121635177</v>
       </c>
       <c r="B14" t="n">
-        <v>56259</v>
+        <v>56276</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2142,30 +2142,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R14" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2224,17 +2224,17 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,10 +2261,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121635184</v>
+        <v>121635217</v>
       </c>
       <c r="B15" t="n">
-        <v>56276</v>
+        <v>56266</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2277,26 +2277,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,10 +2392,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121635164</v>
+        <v>121635195</v>
       </c>
       <c r="B16" t="n">
-        <v>56278</v>
+        <v>56273</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2408,26 +2408,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R16" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2481,22 +2481,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2523,14 +2523,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121635219</v>
+        <v>121635239</v>
       </c>
       <c r="B17" t="n">
-        <v>56259</v>
+        <v>56257</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2539,26 +2539,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R17" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2617,17 +2617,17 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2654,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121635201</v>
+        <v>121635228</v>
       </c>
       <c r="B18" t="n">
-        <v>56273</v>
+        <v>56259</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2666,30 +2666,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121635217</v>
+        <v>121635164</v>
       </c>
       <c r="B19" t="n">
-        <v>56266</v>
+        <v>56278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2801,26 +2801,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R19" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2879,17 +2879,17 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2916,7 +2916,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121635239</v>
+        <v>121635231</v>
       </c>
       <c r="B20" t="n">
         <v>56257</v>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2975,13 +2975,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R20" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3010,17 +3010,17 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3178,10 +3178,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121635177</v>
+        <v>121635169</v>
       </c>
       <c r="B22" t="n">
-        <v>56276</v>
+        <v>56278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3194,26 +3194,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R22" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3267,22 +3267,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3440,42 +3440,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121635231</v>
+        <v>121635184</v>
       </c>
       <c r="B24" t="n">
-        <v>56257</v>
+        <v>56276</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100015</v>
+        <v>100111</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3499,13 +3499,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R24" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3529,22 +3529,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121635169</v>
+        <v>121635219</v>
       </c>
       <c r="B25" t="n">
-        <v>56278</v>
+        <v>56259</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3583,30 +3583,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3630,13 +3630,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R25" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3660,22 +3660,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -2130,7 +2130,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121635177</v>
+        <v>121635184</v>
       </c>
       <c r="B14" t="n">
         <v>56276</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R14" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,22 +2219,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,10 +2261,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121635217</v>
+        <v>121635164</v>
       </c>
       <c r="B15" t="n">
-        <v>56266</v>
+        <v>56278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2277,26 +2277,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R15" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2355,17 +2355,17 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,10 +2392,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121635195</v>
+        <v>121635177</v>
       </c>
       <c r="B16" t="n">
-        <v>56273</v>
+        <v>56276</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2408,26 +2408,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R16" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2481,22 +2481,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2523,14 +2523,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121635239</v>
+        <v>121635219</v>
       </c>
       <c r="B17" t="n">
-        <v>56257</v>
+        <v>56259</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2539,26 +2539,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R17" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2617,17 +2617,17 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2654,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121635228</v>
+        <v>121635214</v>
       </c>
       <c r="B18" t="n">
-        <v>56259</v>
+        <v>56266</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2666,30 +2666,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2743,22 +2743,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2785,7 +2785,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121635164</v>
+        <v>121635169</v>
       </c>
       <c r="B19" t="n">
         <v>56278</v>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R19" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2874,22 +2874,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2916,32 +2916,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121635231</v>
+        <v>121635201</v>
       </c>
       <c r="B20" t="n">
-        <v>56257</v>
+        <v>56273</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100015</v>
+        <v>100092</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2975,13 +2975,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R20" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3010,17 +3010,17 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3047,32 +3047,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121635190</v>
+        <v>121635234</v>
       </c>
       <c r="B21" t="n">
-        <v>56273</v>
+        <v>56257</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100092</v>
+        <v>100015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3106,13 +3106,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R21" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3136,22 +3136,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3178,42 +3178,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121635169</v>
+        <v>121635231</v>
       </c>
       <c r="B22" t="n">
-        <v>56278</v>
+        <v>56257</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205995</v>
+        <v>100015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R22" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3267,22 +3267,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3440,10 +3440,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121635184</v>
+        <v>121635190</v>
       </c>
       <c r="B24" t="n">
-        <v>56276</v>
+        <v>56273</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3456,26 +3456,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3499,13 +3499,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R24" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3529,22 +3529,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3571,7 +3571,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121635219</v>
+        <v>121635228</v>
       </c>
       <c r="B25" t="n">
         <v>56259</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3630,13 +3630,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R25" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>04:50</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -3050,11 +3050,11 @@
         <v>121635234</v>
       </c>
       <c r="B21" t="n">
-        <v>56257</v>
+        <v>56269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3181,11 +3181,11 @@
         <v>121635231</v>
       </c>
       <c r="B22" t="n">
-        <v>56257</v>
+        <v>56269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -3065,11 +3065,6 @@
       <c r="E21" t="n">
         <v>100015</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Barbastell</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Barbastella barbastellus</t>
@@ -3195,11 +3190,6 @@
       </c>
       <c r="E22" t="n">
         <v>100015</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Barbastell</t>
-        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -3050,7 +3050,7 @@
         <v>121635234</v>
       </c>
       <c r="B21" t="n">
-        <v>56269</v>
+        <v>56273</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3064,6 +3064,11 @@
       </c>
       <c r="E21" t="n">
         <v>100015</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3176,7 +3181,7 @@
         <v>121635231</v>
       </c>
       <c r="B22" t="n">
-        <v>56269</v>
+        <v>56273</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3190,6 +3195,11 @@
       </c>
       <c r="E22" t="n">
         <v>100015</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen</t>
+          <t>Johanna Kammonen, Isabella Honnér</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen</t>
+          <t>Johanna Kammonen, Isabella Honnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johanna Kammonen, Isabella Honnér</t>
+          <t>Isabella Honnér, Johanna Kammonen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johanna Kammonen, Isabella Honnér</t>
+          <t>Isabella Honnér, Johanna Kammonen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -3050,7 +3050,7 @@
         <v>121635234</v>
       </c>
       <c r="B21" t="n">
-        <v>56273</v>
+        <v>56274</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>121635231</v>
       </c>
       <c r="B22" t="n">
-        <v>56273</v>
+        <v>56274</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -3050,7 +3050,7 @@
         <v>121635234</v>
       </c>
       <c r="B21" t="n">
-        <v>56274</v>
+        <v>56368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen</t>
+          <t>Johanna Kammonen, Isabella Honnér</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3181,7 +3181,7 @@
         <v>121635231</v>
       </c>
       <c r="B22" t="n">
-        <v>56274</v>
+        <v>56368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen</t>
+          <t>Johanna Kammonen, Isabella Honnér</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,67 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113899922</v>
+        <v>121635231</v>
       </c>
       <c r="B2" t="n">
-        <v>104650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>100015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Karsholms fure, Sk</t>
+          <t>Karsholm, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455875</v>
+        <v>456110</v>
       </c>
       <c r="R2" t="n">
-        <v>6215774</v>
+        <v>6215684</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,78 +789,79 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>André Dabolins</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Alight - NVI Karsholm</t>
-        </is>
-      </c>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113899923</v>
+        <v>121635234</v>
       </c>
       <c r="B3" t="n">
-        <v>104650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>100015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Karsholms fure, Sk</t>
+          <t>Karsholm, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455871</v>
+        <v>455851</v>
       </c>
       <c r="R3" t="n">
-        <v>6215751</v>
+        <v>6215609</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +885,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,31 +915,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>André Dabolins</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Alight - NVI Karsholm</t>
-        </is>
-      </c>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113899921</v>
+        <v>119439603</v>
       </c>
       <c r="B4" t="n">
-        <v>104650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,31 +938,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>100038</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,10 +976,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455876</v>
+        <v>455890</v>
       </c>
       <c r="R4" t="n">
-        <v>6215782</v>
+        <v>6215765</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1004,22 +1006,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:50</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,26 +1031,21 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Alight - NVI Karsholm</t>
+          <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113899920</v>
+        <v>119439586</v>
       </c>
       <c r="B5" t="n">
-        <v>104650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,31 +1053,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221141</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,13 +1086,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455881</v>
+        <v>456272</v>
       </c>
       <c r="R5" t="n">
-        <v>6215698</v>
+        <v>6215678</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1116,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,26 +1141,21 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Alight - NVI Karsholm</t>
+          <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119438416</v>
+        <v>98294816</v>
       </c>
       <c r="B6" t="n">
-        <v>57679</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,16 +1163,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100088</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1208,34 +1180,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Karsholms fure, Sk</t>
+          <t>Karsholms Fure, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456188</v>
+        <v>455938</v>
       </c>
       <c r="R6" t="n">
-        <v>6215696</v>
+        <v>6215830</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,12 +1234,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2021-05-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2021-05-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,37 +1248,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Mattias Göransson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Alight - Karsholm fågelinventering</t>
-        </is>
-      </c>
+          <t>Mattias Göransson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119439317</v>
+        <v>121635190</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,51 +1278,56 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Karsholms fure, Sk</t>
+          <t>Karsholm, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456113</v>
+        <v>456110</v>
       </c>
       <c r="R7" t="n">
-        <v>6215706</v>
+        <v>6215684</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,12 +1351,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,31 +1381,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>André Dabolins</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Alight - Karsholm fågelinventering</t>
-        </is>
-      </c>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119439297</v>
+        <v>121635195</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,51 +1404,56 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102990</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Karsholms fure, Sk</t>
+          <t>Karsholm, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456069</v>
+        <v>455851</v>
       </c>
       <c r="R8" t="n">
-        <v>6215708</v>
+        <v>6215609</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,12 +1477,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,31 +1507,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>André Dabolins</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Alight - Karsholm fågelinventering</t>
-        </is>
-      </c>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119439603</v>
+        <v>121635177</v>
       </c>
       <c r="B9" t="n">
-        <v>56621</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,21 +1530,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100038</v>
+        <v>100111</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1573,29 +1552,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Karsholms fure, Sk</t>
+          <t>Karsholm, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455890</v>
+        <v>456110</v>
       </c>
       <c r="R9" t="n">
-        <v>6215765</v>
+        <v>6215684</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,12 +1603,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,83 +1633,79 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>André Dabolins</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Alight - Karsholm fågelinventering</t>
-        </is>
-      </c>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119438373</v>
+        <v>121635184</v>
       </c>
       <c r="B10" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103020</v>
+        <v>100111</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karsholms fure, Sk</t>
+          <t>Karsholm, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455951</v>
+        <v>455851</v>
       </c>
       <c r="R10" t="n">
-        <v>6215702</v>
+        <v>6215609</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1739,12 +1729,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,35 +1759,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>André Dabolins</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Alight - Karsholm fågelinventering</t>
-        </is>
-      </c>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119439330</v>
+        <v>119439294</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1829,13 +1820,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455929</v>
+        <v>455972</v>
       </c>
       <c r="R11" t="n">
-        <v>6215668</v>
+        <v>6215607</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1859,12 +1850,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,19 +1886,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119439294</v>
+        <v>119439297</v>
       </c>
       <c r="B12" t="n">
-        <v>57851</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1949,10 +1935,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455972</v>
+        <v>456069</v>
       </c>
       <c r="R12" t="n">
-        <v>6215607</v>
+        <v>6215708</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
@@ -2015,32 +2001,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119437912</v>
+        <v>119439315</v>
       </c>
       <c r="B13" t="n">
-        <v>57986</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2053,9 +2034,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2064,13 +2050,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455891</v>
+        <v>456201</v>
       </c>
       <c r="R13" t="n">
-        <v>6215754</v>
+        <v>6215713</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2094,12 +2080,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,7 +2105,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2130,72 +2116,62 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121635184</v>
+        <v>119439317</v>
       </c>
       <c r="B14" t="n">
-        <v>56276</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100111</v>
+        <v>102990</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Karsholm, Sk</t>
+          <t>Karsholms fure, Sk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455851</v>
+        <v>456113</v>
       </c>
       <c r="R14" t="n">
-        <v>6215609</v>
+        <v>6215706</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,22 +2195,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>06:30</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2249,84 +2215,78 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>André Dabolins</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Angelia Ellvin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Alight - Karsholm fågelinventering</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121635164</v>
+        <v>119439330</v>
       </c>
       <c r="B15" t="n">
-        <v>56278</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205995</v>
+        <v>102990</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karsholm, Sk</t>
+          <t>Karsholms fure, Sk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456110</v>
+        <v>455929</v>
       </c>
       <c r="R15" t="n">
-        <v>6215684</v>
+        <v>6215668</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2350,22 +2310,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>21:40</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:40</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2380,27 +2330,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>André Dabolins</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Engla Grönvall</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Alight - Karsholm fågelinventering</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121635177</v>
+        <v>119438416</v>
       </c>
       <c r="B16" t="n">
-        <v>56276</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,21 +2357,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100111</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2430,34 +2379,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Karsholm, Sk</t>
+          <t>Karsholms fure, Sk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456110</v>
+        <v>456188</v>
       </c>
       <c r="R16" t="n">
-        <v>6215684</v>
+        <v>6215696</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2481,22 +2425,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>21:40</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:40</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2511,84 +2445,73 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>André Dabolins</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Angelia Ellvin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Alight - Karsholm fågelinventering</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121635219</v>
+        <v>119438424</v>
       </c>
       <c r="B17" t="n">
-        <v>56259</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Karsholm, Sk</t>
+          <t>Karsholms fure, Sk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456110</v>
+        <v>455848</v>
       </c>
       <c r="R17" t="n">
-        <v>6215684</v>
+        <v>6215580</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2612,22 +2535,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>21:40</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:40</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2642,49 +2555,48 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>André Dabolins</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Angelia Ellvin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Alight - Karsholm fågelinventering</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121635214</v>
+        <v>119438373</v>
       </c>
       <c r="B18" t="n">
-        <v>56266</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205992</v>
+        <v>103020</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2692,34 +2604,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Karsholm, Sk</t>
+          <t>Karsholms fure, Sk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455851</v>
+        <v>455951</v>
       </c>
       <c r="R18" t="n">
-        <v>6215609</v>
+        <v>6215702</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2743,22 +2650,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>06:30</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2773,84 +2670,78 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>André Dabolins</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Engla Grönvall</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Alight - Karsholm fågelinventering</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121635169</v>
+        <v>119438365</v>
       </c>
       <c r="B19" t="n">
-        <v>56278</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205995</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Karsholm, Sk</t>
+          <t>Karsholms fure, Sk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455851</v>
+        <v>456235</v>
       </c>
       <c r="R19" t="n">
-        <v>6215609</v>
+        <v>6215719</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2874,22 +2765,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>06:30</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2904,27 +2785,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>André Dabolins</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Angelia Ellvin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Alight - Karsholm fågelinventering</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121635201</v>
+        <v>119437912</v>
       </c>
       <c r="B20" t="n">
-        <v>56273</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2932,56 +2812,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100092</v>
+        <v>103044</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Karsholm, Sk</t>
+          <t>Karsholms fure, Sk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455851</v>
+        <v>455891</v>
       </c>
       <c r="R20" t="n">
-        <v>6215609</v>
+        <v>6215754</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3005,22 +2875,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>04:50</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3035,84 +2895,73 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>André Dabolins</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Engla Grönvall</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Alight - Karsholm fågelinventering</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121635234</v>
+        <v>115184340</v>
       </c>
       <c r="B21" t="n">
-        <v>56368</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100015</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Karsholm, Sk</t>
+          <t>Karsholms fure, Sk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455851</v>
+        <v>455860</v>
       </c>
       <c r="R21" t="n">
-        <v>6215609</v>
+        <v>6215781</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3136,22 +2985,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3166,49 +3015,48 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>André Dabolins</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isabella Honnér, Johanna Kammonen</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Agnes Eriksson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Alight - NVI Karsholm</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121635231</v>
+        <v>121635214</v>
       </c>
       <c r="B22" t="n">
-        <v>56368</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100015</v>
+        <v>205992</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3228,7 +3076,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3237,13 +3085,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R22" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3267,22 +3115,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3309,42 +3157,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121635161</v>
+        <v>121635164</v>
       </c>
       <c r="B23" t="n">
-        <v>56280</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3359,7 +3202,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3368,13 +3211,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R23" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3398,22 +3241,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3440,15 +3283,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121635190</v>
+        <v>121635169</v>
       </c>
       <c r="B24" t="n">
-        <v>56273</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3456,26 +3294,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3490,7 +3328,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BatLogger</t>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3499,13 +3337,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456110</v>
+        <v>455851</v>
       </c>
       <c r="R24" t="n">
-        <v>6215684</v>
+        <v>6215609</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3529,22 +3367,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3571,15 +3409,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121635228</v>
+        <v>121635219</v>
       </c>
       <c r="B25" t="n">
-        <v>56259</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3606,7 +3439,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3621,7 +3454,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3630,13 +3463,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455851</v>
+        <v>456110</v>
       </c>
       <c r="R25" t="n">
-        <v>6215609</v>
+        <v>6215684</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3665,17 +3498,17 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>04:50</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3699,6 +3532,839 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121635228</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>455851</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6215609</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>04:50</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121635161</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Karsholm, Sk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>455851</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6215609</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>André Dabolins</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Isabella Honnér, Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>113899920</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Karsholms fure, Sk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>455881</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6215698</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Alight - NVI Karsholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>113899921</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Karsholms fure, Sk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>455876</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6215782</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Alight - NVI Karsholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>113899922</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Karsholms fure, Sk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>455875</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6215774</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Alight - NVI Karsholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>113899923</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Karsholms fure, Sk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>455871</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6215751</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Alight - NVI Karsholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>107655948</v>
+      </c>
+      <c r="B32" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Karsholms fure, Sk</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>455843</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6215592</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Alight - NVI Karsholm</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52019-2021 artfynd.xlsx
+++ b/artfynd/A 52019-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635231</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635234</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1039,6 +1054,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119439603</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,6 +1169,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119439586</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98294816</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1390,6 +1420,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635190</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1516,6 +1551,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635195</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1642,6 +1682,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635177</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1768,6 +1813,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635184</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1883,6 +1933,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119439294</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1998,6 +2053,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119439297</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2113,6 +2173,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119439315</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2228,6 +2293,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119439317</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2343,6 +2413,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119439330</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2458,6 +2533,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119438416</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2568,6 +2648,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119438424</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2683,6 +2768,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119438373</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2798,6 +2888,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119438365</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2908,6 +3003,11 @@
           <t>Alight - Karsholm fågelinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119437912</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3028,6 +3128,11 @@
           <t>Alight - NVI Karsholm</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115184340</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3154,6 +3259,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635214</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3280,6 +3390,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635164</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3406,6 +3521,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635169</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3532,6 +3652,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635219</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3658,6 +3783,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635228</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3784,6 +3914,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121635161</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3904,6 +4039,11 @@
           <t>Alight - NVI Karsholm</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113899920</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4024,6 +4164,11 @@
           <t>Alight - NVI Karsholm</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113899921</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4144,6 +4289,11 @@
           <t>Alight - NVI Karsholm</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113899922</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4264,6 +4414,11 @@
           <t>Alight - NVI Karsholm</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113899923</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4365,8 +4520,46 @@
           <t>Alight - NVI Karsholm</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107655948</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>